--- a/RPI.xlsx
+++ b/RPI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0eb6a9f0be765fac/Pulpit/inwestycje/modele/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2001s\modele\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="300" documentId="8_{9F476FD2-9FA6-475A-9F72-CC452AF4AAE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B498629-8851-46FD-8F3B-C56F9F232625}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB2B437-E31D-4A86-B91E-A6BFDBED1E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{E98EB17B-F02A-46E8-ACDF-C760F78E9737}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{E98EB17B-F02A-46E8-ACDF-C760F78E9737}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>Price</t>
   </si>
@@ -114,9 +114,6 @@
     <t>FCF</t>
   </si>
   <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
     <t>Discount rate</t>
   </si>
   <si>
@@ -126,18 +123,25 @@
     <t>share</t>
   </si>
   <si>
-    <t>Q125</t>
-  </si>
-  <si>
     <t>Net Margin</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Inventory</t>
+  </si>
+  <si>
+    <t>terminal value</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -177,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -185,6 +189,9 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -206,16 +213,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -230,8 +237,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6124575" y="38100"/>
-          <a:ext cx="19050" cy="10629900"/>
+          <a:off x="7343775" y="47625"/>
+          <a:ext cx="19050" cy="10820400"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -574,55 +581,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCC3D5B2-4C70-4AEF-9DFB-79A58BD75B45}">
-  <dimension ref="J1:N7"/>
+  <dimension ref="J2:L7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="M1" t="s">
-        <v>25</v>
-      </c>
-      <c r="N1">
-        <v>1.2589999999999999</v>
-      </c>
-    </row>
-    <row r="2" spans="10:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J2" t="s">
         <v>0</v>
       </c>
       <c r="K2" s="4">
-        <f>6.02*N1</f>
-        <v>7.5791799999999991</v>
+        <v>6.64</v>
       </c>
       <c r="L2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="10:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J3" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="1">
-        <v>193.42</v>
-      </c>
-    </row>
-    <row r="4" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="K3">
+        <v>198.7</v>
+      </c>
+    </row>
+    <row r="4" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J4" t="s">
         <v>2</v>
       </c>
       <c r="K4" s="1">
         <f>K3*K2</f>
-        <v>1465.9649955999998</v>
-      </c>
-    </row>
-    <row r="5" spans="10:14" x14ac:dyDescent="0.25">
+        <v>1319.3679999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J5" t="s">
         <v>3</v>
       </c>
       <c r="K5">
-        <v>40.4</v>
-      </c>
-    </row>
-    <row r="6" spans="10:14" x14ac:dyDescent="0.25">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="6" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J6" t="s">
         <v>4</v>
       </c>
@@ -630,13 +628,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="10:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J7" t="s">
         <v>5</v>
       </c>
       <c r="K7" s="1">
         <f>K4-K5+K6</f>
-        <v>1425.5649955999997</v>
+        <v>1290.9679999999998</v>
       </c>
     </row>
   </sheetData>
@@ -646,10 +644,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E15DC23F-DC20-407B-BB0E-87053752C463}">
-  <dimension ref="A2:DU26"/>
+  <dimension ref="A2:DU34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="0" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -679,16 +678,16 @@
       <c r="L2">
         <v>2026</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="9">
         <v>2027</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="9">
         <v>2028</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="9">
         <v>2029</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="9">
         <v>2030</v>
       </c>
     </row>
@@ -712,12 +711,30 @@
         <v>265.8</v>
       </c>
       <c r="J3" s="2">
-        <f>J5/0.244</f>
-        <v>266.80327868852459</v>
+        <v>259.5</v>
       </c>
       <c r="K3" s="2">
-        <f>K5/0.253</f>
-        <v>305.13833992094862</v>
+        <v>323.2</v>
+      </c>
+      <c r="L3" s="2">
+        <f>256.9*2.1</f>
+        <v>539.49</v>
+      </c>
+      <c r="M3" s="7">
+        <f>L3*1.6</f>
+        <v>863.18400000000008</v>
+      </c>
+      <c r="N3" s="7">
+        <f>M3*1.6</f>
+        <v>1381.0944000000002</v>
+      </c>
+      <c r="O3" s="7">
+        <f>N3*1.6</f>
+        <v>2209.7510400000006</v>
+      </c>
+      <c r="P3" s="7">
+        <f>O3*1.6</f>
+        <v>3535.6016640000012</v>
       </c>
     </row>
     <row r="4" spans="1:125" x14ac:dyDescent="0.25">
@@ -739,6 +756,32 @@
       <c r="I4">
         <v>199.84</v>
       </c>
+      <c r="J4">
+        <v>196.3</v>
+      </c>
+      <c r="K4">
+        <v>245.4</v>
+      </c>
+      <c r="L4">
+        <f>197.5*2.1</f>
+        <v>414.75</v>
+      </c>
+      <c r="M4" s="4">
+        <f>M3*(1-0.24)</f>
+        <v>656.01984000000004</v>
+      </c>
+      <c r="N4" s="4">
+        <f>N3*(1-0.24)</f>
+        <v>1049.6317440000003</v>
+      </c>
+      <c r="O4" s="4">
+        <f>O3*(1-0.24)</f>
+        <v>1679.4107904000005</v>
+      </c>
+      <c r="P4" s="4">
+        <f>P3*(1-0.24)</f>
+        <v>2687.057264640001</v>
+      </c>
     </row>
     <row r="5" spans="1:125" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -765,10 +808,32 @@
         <v>65.960000000000008</v>
       </c>
       <c r="J5">
-        <v>65.099999999999994</v>
+        <f>J3-J4</f>
+        <v>63.199999999999989</v>
       </c>
       <c r="K5">
-        <v>77.2</v>
+        <f>K3-K4</f>
+        <v>77.799999999999983</v>
+      </c>
+      <c r="L5">
+        <f>L3-L4</f>
+        <v>124.74000000000001</v>
+      </c>
+      <c r="M5" s="4">
+        <f>M3-M4</f>
+        <v>207.16416000000004</v>
+      </c>
+      <c r="N5" s="4">
+        <f>N3-N4</f>
+        <v>331.46265599999992</v>
+      </c>
+      <c r="O5" s="4">
+        <f>O3-O4</f>
+        <v>530.34024960000011</v>
+      </c>
+      <c r="P5" s="4">
+        <f>P3-P4</f>
+        <v>848.54439936000017</v>
       </c>
     </row>
     <row r="6" spans="1:125" x14ac:dyDescent="0.25">
@@ -790,6 +855,31 @@
       <c r="I6">
         <v>17.63</v>
       </c>
+      <c r="J6">
+        <v>24.8</v>
+      </c>
+      <c r="K6">
+        <v>27.6</v>
+      </c>
+      <c r="L6">
+        <v>46</v>
+      </c>
+      <c r="M6" s="4">
+        <f>L6*1.2</f>
+        <v>55.199999999999996</v>
+      </c>
+      <c r="N6" s="4">
+        <f>M6*1.2</f>
+        <v>66.239999999999995</v>
+      </c>
+      <c r="O6" s="4">
+        <f>N6*1.2</f>
+        <v>79.487999999999985</v>
+      </c>
+      <c r="P6" s="4">
+        <f>O6*1.2</f>
+        <v>95.385599999999982</v>
+      </c>
     </row>
     <row r="7" spans="1:125" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -810,6 +900,31 @@
       <c r="I7">
         <v>10.58</v>
       </c>
+      <c r="J7">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="K7">
+        <v>22.5</v>
+      </c>
+      <c r="L7">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="M7" s="4">
+        <f>L7*1.6</f>
+        <v>53.120000000000005</v>
+      </c>
+      <c r="N7" s="4">
+        <f>M7*1.6</f>
+        <v>84.992000000000019</v>
+      </c>
+      <c r="O7" s="4">
+        <f>N7*1.6</f>
+        <v>135.98720000000003</v>
+      </c>
+      <c r="P7" s="4">
+        <f>O7*1.6</f>
+        <v>217.57952000000006</v>
+      </c>
     </row>
     <row r="8" spans="1:125" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -835,6 +950,34 @@
         <f>SUM(I6:I7)</f>
         <v>28.21</v>
       </c>
+      <c r="J8">
+        <f>SUM(J6:J7)</f>
+        <v>42.7</v>
+      </c>
+      <c r="K8">
+        <f>SUM(K6:K7)</f>
+        <v>50.1</v>
+      </c>
+      <c r="L8">
+        <f>SUM(L6:L7)</f>
+        <v>79.2</v>
+      </c>
+      <c r="M8" s="4">
+        <f>SUM(M6:M7)</f>
+        <v>108.32</v>
+      </c>
+      <c r="N8" s="4">
+        <f>SUM(N6:N7)</f>
+        <v>151.23200000000003</v>
+      </c>
+      <c r="O8" s="4">
+        <f>SUM(O6:O7)</f>
+        <v>215.47520000000003</v>
+      </c>
+      <c r="P8" s="4">
+        <f>SUM(P6:P7)</f>
+        <v>312.96512000000007</v>
+      </c>
     </row>
     <row r="9" spans="1:125" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -860,6 +1003,34 @@
         <f>I5-I8</f>
         <v>37.750000000000007</v>
       </c>
+      <c r="J9">
+        <f>J5-J8</f>
+        <v>20.499999999999986</v>
+      </c>
+      <c r="K9">
+        <f>K5-K8</f>
+        <v>27.699999999999982</v>
+      </c>
+      <c r="L9">
+        <f>L5-L8</f>
+        <v>45.540000000000006</v>
+      </c>
+      <c r="M9" s="4">
+        <f>M5-M8</f>
+        <v>98.844160000000045</v>
+      </c>
+      <c r="N9" s="4">
+        <f>N5-N8</f>
+        <v>180.2306559999999</v>
+      </c>
+      <c r="O9" s="4">
+        <f>O5-O8</f>
+        <v>314.86504960000008</v>
+      </c>
+      <c r="P9" s="4">
+        <f>P5-P8</f>
+        <v>535.5792793600001</v>
+      </c>
     </row>
     <row r="10" spans="1:125" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -883,6 +1054,34 @@
         <f>-0.48+1.44-0.49</f>
         <v>0.47</v>
       </c>
+      <c r="J10">
+        <f>1.1-1.2</f>
+        <v>-9.9999999999999867E-2</v>
+      </c>
+      <c r="K10">
+        <f>1-1.4</f>
+        <v>-0.39999999999999991</v>
+      </c>
+      <c r="L10" s="8">
+        <f>-0.4</f>
+        <v>-0.4</v>
+      </c>
+      <c r="M10" s="8">
+        <f>-0.4</f>
+        <v>-0.4</v>
+      </c>
+      <c r="N10" s="8">
+        <f>-0.4</f>
+        <v>-0.4</v>
+      </c>
+      <c r="O10" s="8">
+        <f>-0.4</f>
+        <v>-0.4</v>
+      </c>
+      <c r="P10" s="8">
+        <f>-0.4</f>
+        <v>-0.4</v>
+      </c>
     </row>
     <row r="11" spans="1:125" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -908,6 +1107,34 @@
         <f>I9-I10</f>
         <v>37.280000000000008</v>
       </c>
+      <c r="J11">
+        <f>J9-J10</f>
+        <v>20.599999999999987</v>
+      </c>
+      <c r="K11">
+        <f>K9-K10</f>
+        <v>28.09999999999998</v>
+      </c>
+      <c r="L11" s="4">
+        <f>L9-L10</f>
+        <v>45.940000000000005</v>
+      </c>
+      <c r="M11" s="4">
+        <f>M9-M10</f>
+        <v>99.244160000000051</v>
+      </c>
+      <c r="N11" s="4">
+        <f>N9-N10</f>
+        <v>180.6306559999999</v>
+      </c>
+      <c r="O11" s="4">
+        <f>O9-O10</f>
+        <v>315.26504960000005</v>
+      </c>
+      <c r="P11" s="4">
+        <f>P9-P10</f>
+        <v>535.97927936000008</v>
+      </c>
     </row>
     <row r="12" spans="1:125" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -928,6 +1155,31 @@
       <c r="I12">
         <v>6.62</v>
       </c>
+      <c r="J12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="K12">
+        <v>4.8</v>
+      </c>
+      <c r="L12" s="4">
+        <v>5</v>
+      </c>
+      <c r="M12" s="4">
+        <f>0.16*M11</f>
+        <v>15.879065600000008</v>
+      </c>
+      <c r="N12" s="4">
+        <f>0.16*N11</f>
+        <v>28.900904959999984</v>
+      </c>
+      <c r="O12" s="4">
+        <f>0.16*O11</f>
+        <v>50.442407936000009</v>
+      </c>
+      <c r="P12" s="4">
+        <f>0.16*P11</f>
+        <v>85.756684697600008</v>
+      </c>
     </row>
     <row r="13" spans="1:125" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -953,469 +1205,469 @@
         <f>I11-I12</f>
         <v>30.660000000000007</v>
       </c>
-      <c r="J13" s="4">
-        <f>0.12*J3</f>
-        <v>32.016393442622949</v>
-      </c>
-      <c r="K13" s="4">
-        <f>0.12*K3</f>
-        <v>36.616600790513836</v>
+      <c r="J13">
+        <f>J11-J12</f>
+        <v>15.999999999999988</v>
+      </c>
+      <c r="K13">
+        <f>K11-K12</f>
+        <v>23.299999999999979</v>
       </c>
       <c r="L13" s="4">
-        <f t="shared" ref="L13:P13" si="0">K13*1.2</f>
-        <v>43.939920948616603</v>
+        <f>L11-L12</f>
+        <v>40.940000000000005</v>
       </c>
       <c r="M13" s="4">
-        <f t="shared" si="0"/>
-        <v>52.727905138339921</v>
+        <f>M11-M12</f>
+        <v>83.365094400000046</v>
       </c>
       <c r="N13" s="4">
-        <f t="shared" si="0"/>
-        <v>63.273486166007899</v>
+        <f>N11-N12</f>
+        <v>151.72975103999991</v>
       </c>
       <c r="O13" s="4">
-        <f t="shared" si="0"/>
-        <v>75.928183399209473</v>
+        <f>O11-O12</f>
+        <v>264.82264166400006</v>
       </c>
       <c r="P13" s="4">
-        <f t="shared" si="0"/>
-        <v>91.113820079051365</v>
+        <f>P11-P12</f>
+        <v>450.22259466240007</v>
       </c>
       <c r="Q13">
-        <f>P13*0.99</f>
-        <v>90.202681878260847</v>
+        <f>P13*(1+$O$31)</f>
+        <v>445.72036871577609</v>
       </c>
       <c r="R13">
-        <f t="shared" ref="R13:CC13" si="1">Q13*0.99</f>
-        <v>89.300655059478231</v>
+        <f t="shared" ref="R13:CC13" si="0">Q13*(1+$O$31)</f>
+        <v>441.26316502861835</v>
       </c>
       <c r="S13">
-        <f t="shared" si="1"/>
-        <v>88.407648508883454</v>
+        <f t="shared" si="0"/>
+        <v>436.85053337833216</v>
       </c>
       <c r="T13">
-        <f t="shared" si="1"/>
-        <v>87.523572023794614</v>
+        <f t="shared" si="0"/>
+        <v>432.48202804454883</v>
       </c>
       <c r="U13">
-        <f t="shared" si="1"/>
-        <v>86.648336303556661</v>
+        <f t="shared" si="0"/>
+        <v>428.15720776410336</v>
       </c>
       <c r="V13">
-        <f t="shared" si="1"/>
-        <v>85.781852940521091</v>
+        <f t="shared" si="0"/>
+        <v>423.87563568646232</v>
       </c>
       <c r="W13">
-        <f t="shared" si="1"/>
-        <v>84.924034411115883</v>
+        <f t="shared" si="0"/>
+        <v>419.63687932959772</v>
       </c>
       <c r="X13">
-        <f t="shared" si="1"/>
-        <v>84.074794067004717</v>
+        <f t="shared" si="0"/>
+        <v>415.44051053630176</v>
       </c>
       <c r="Y13">
-        <f t="shared" si="1"/>
-        <v>83.234046126334675</v>
+        <f t="shared" si="0"/>
+        <v>411.28610543093873</v>
       </c>
       <c r="Z13">
-        <f t="shared" si="1"/>
-        <v>82.401705665071333</v>
+        <f t="shared" si="0"/>
+        <v>407.17324437662933</v>
       </c>
       <c r="AA13">
-        <f t="shared" si="1"/>
-        <v>81.577688608420615</v>
+        <f t="shared" si="0"/>
+        <v>403.10151193286305</v>
       </c>
       <c r="AB13">
-        <f t="shared" si="1"/>
-        <v>80.761911722336407</v>
+        <f t="shared" si="0"/>
+        <v>399.07049681353442</v>
       </c>
       <c r="AC13">
-        <f t="shared" si="1"/>
-        <v>79.954292605113039</v>
+        <f t="shared" si="0"/>
+        <v>395.07979184539909</v>
       </c>
       <c r="AD13">
-        <f t="shared" si="1"/>
-        <v>79.154749679061908</v>
+        <f t="shared" si="0"/>
+        <v>391.1289939269451</v>
       </c>
       <c r="AE13">
-        <f t="shared" si="1"/>
-        <v>78.363202182271294</v>
+        <f t="shared" si="0"/>
+        <v>387.21770398767563</v>
       </c>
       <c r="AF13">
-        <f t="shared" si="1"/>
-        <v>77.579570160448583</v>
+        <f t="shared" si="0"/>
+        <v>383.34552694779887</v>
       </c>
       <c r="AG13">
-        <f t="shared" si="1"/>
-        <v>76.803774458844103</v>
+        <f t="shared" si="0"/>
+        <v>379.51207167832086</v>
       </c>
       <c r="AH13">
-        <f t="shared" si="1"/>
-        <v>76.035736714255663</v>
+        <f t="shared" si="0"/>
+        <v>375.71695096153763</v>
       </c>
       <c r="AI13">
-        <f t="shared" si="1"/>
-        <v>75.275379347113102</v>
+        <f t="shared" si="0"/>
+        <v>371.95978145192225</v>
       </c>
       <c r="AJ13">
-        <f t="shared" si="1"/>
-        <v>74.522625553641973</v>
+        <f t="shared" si="0"/>
+        <v>368.24018363740305</v>
       </c>
       <c r="AK13">
-        <f t="shared" si="1"/>
-        <v>73.77739929810555</v>
+        <f t="shared" si="0"/>
+        <v>364.55778180102902</v>
       </c>
       <c r="AL13">
-        <f t="shared" si="1"/>
-        <v>73.039625305124488</v>
+        <f t="shared" si="0"/>
+        <v>360.91220398301874</v>
       </c>
       <c r="AM13">
-        <f t="shared" si="1"/>
-        <v>72.309229052073249</v>
+        <f t="shared" si="0"/>
+        <v>357.30308194318854</v>
       </c>
       <c r="AN13">
-        <f t="shared" si="1"/>
-        <v>71.58613676155251</v>
+        <f t="shared" si="0"/>
+        <v>353.73005112375665</v>
       </c>
       <c r="AO13">
-        <f t="shared" si="1"/>
-        <v>70.870275393936979</v>
+        <f t="shared" si="0"/>
+        <v>350.19275061251909</v>
       </c>
       <c r="AP13">
-        <f t="shared" si="1"/>
-        <v>70.161572639997601</v>
+        <f t="shared" si="0"/>
+        <v>346.69082310639391</v>
       </c>
       <c r="AQ13">
-        <f t="shared" si="1"/>
-        <v>69.459956913597622</v>
+        <f t="shared" si="0"/>
+        <v>343.22391487532997</v>
       </c>
       <c r="AR13">
-        <f t="shared" si="1"/>
-        <v>68.765357344461648</v>
+        <f t="shared" si="0"/>
+        <v>339.79167572657667</v>
       </c>
       <c r="AS13">
-        <f t="shared" si="1"/>
-        <v>68.077703771017028</v>
+        <f t="shared" si="0"/>
+        <v>336.39375896931091</v>
       </c>
       <c r="AT13">
-        <f t="shared" si="1"/>
-        <v>67.396926733306856</v>
+        <f t="shared" si="0"/>
+        <v>333.02982137961777</v>
       </c>
       <c r="AU13">
-        <f t="shared" si="1"/>
-        <v>66.722957465973792</v>
+        <f t="shared" si="0"/>
+        <v>329.69952316582157</v>
       </c>
       <c r="AV13">
-        <f t="shared" si="1"/>
-        <v>66.055727891314049</v>
+        <f t="shared" si="0"/>
+        <v>326.40252793416334</v>
       </c>
       <c r="AW13">
-        <f t="shared" si="1"/>
-        <v>65.395170612400904</v>
+        <f t="shared" si="0"/>
+        <v>323.13850265482171</v>
       </c>
       <c r="AX13">
-        <f t="shared" si="1"/>
-        <v>64.741218906276899</v>
+        <f t="shared" si="0"/>
+        <v>319.90711762827351</v>
       </c>
       <c r="AY13">
-        <f t="shared" si="1"/>
-        <v>64.093806717214136</v>
+        <f t="shared" si="0"/>
+        <v>316.70804645199075</v>
       </c>
       <c r="AZ13">
-        <f t="shared" si="1"/>
-        <v>63.452868650041992</v>
+        <f t="shared" si="0"/>
+        <v>313.54096598747083</v>
       </c>
       <c r="BA13">
-        <f t="shared" si="1"/>
-        <v>62.818339963541575</v>
+        <f t="shared" si="0"/>
+        <v>310.40555632759612</v>
       </c>
       <c r="BB13">
-        <f t="shared" si="1"/>
-        <v>62.190156563906157</v>
+        <f t="shared" si="0"/>
+        <v>307.30150076432017</v>
       </c>
       <c r="BC13">
-        <f t="shared" si="1"/>
-        <v>61.568254998267093</v>
+        <f t="shared" si="0"/>
+        <v>304.22848575667695</v>
       </c>
       <c r="BD13">
-        <f t="shared" si="1"/>
-        <v>60.952572448284421</v>
+        <f t="shared" si="0"/>
+        <v>301.18620089911019</v>
       </c>
       <c r="BE13">
-        <f t="shared" si="1"/>
-        <v>60.343046723801578</v>
+        <f t="shared" si="0"/>
+        <v>298.17433889011909</v>
       </c>
       <c r="BF13">
-        <f t="shared" si="1"/>
-        <v>59.739616256563565</v>
+        <f t="shared" si="0"/>
+        <v>295.19259550121791</v>
       </c>
       <c r="BG13">
-        <f t="shared" si="1"/>
-        <v>59.142220093997928</v>
+        <f t="shared" si="0"/>
+        <v>292.24066954620571</v>
       </c>
       <c r="BH13">
-        <f t="shared" si="1"/>
-        <v>58.550797893057947</v>
+        <f t="shared" si="0"/>
+        <v>289.31826285074362</v>
       </c>
       <c r="BI13">
-        <f t="shared" si="1"/>
-        <v>57.965289914127368</v>
+        <f t="shared" si="0"/>
+        <v>286.4250802222362</v>
       </c>
       <c r="BJ13">
-        <f t="shared" si="1"/>
-        <v>57.385637014986095</v>
+        <f t="shared" si="0"/>
+        <v>283.56082942001382</v>
       </c>
       <c r="BK13">
-        <f t="shared" si="1"/>
-        <v>56.811780644836233</v>
+        <f t="shared" si="0"/>
+        <v>280.72522112581368</v>
       </c>
       <c r="BL13">
-        <f t="shared" si="1"/>
-        <v>56.24366283838787</v>
+        <f t="shared" si="0"/>
+        <v>277.91796891455556</v>
       </c>
       <c r="BM13">
-        <f t="shared" si="1"/>
-        <v>55.681226210003992</v>
+        <f t="shared" si="0"/>
+        <v>275.13878922540999</v>
       </c>
       <c r="BN13">
-        <f t="shared" si="1"/>
-        <v>55.124413947903953</v>
+        <f t="shared" si="0"/>
+        <v>272.38740133315588</v>
       </c>
       <c r="BO13">
-        <f t="shared" si="1"/>
-        <v>54.573169808424915</v>
+        <f t="shared" si="0"/>
+        <v>269.66352731982431</v>
       </c>
       <c r="BP13">
-        <f t="shared" si="1"/>
-        <v>54.027438110340668</v>
+        <f t="shared" si="0"/>
+        <v>266.96689204662607</v>
       </c>
       <c r="BQ13">
-        <f t="shared" si="1"/>
-        <v>53.48716372923726</v>
+        <f t="shared" si="0"/>
+        <v>264.29722312615979</v>
       </c>
       <c r="BR13">
-        <f t="shared" si="1"/>
-        <v>52.952292091944884</v>
+        <f t="shared" si="0"/>
+        <v>261.65425089489821</v>
       </c>
       <c r="BS13">
-        <f t="shared" si="1"/>
-        <v>52.422769171025436</v>
+        <f t="shared" si="0"/>
+        <v>259.0377083859492</v>
       </c>
       <c r="BT13">
-        <f t="shared" si="1"/>
-        <v>51.898541479315185</v>
+        <f t="shared" si="0"/>
+        <v>256.44733130208971</v>
       </c>
       <c r="BU13">
-        <f t="shared" si="1"/>
-        <v>51.379556064522035</v>
+        <f t="shared" si="0"/>
+        <v>253.88285798906881</v>
       </c>
       <c r="BV13">
-        <f t="shared" si="1"/>
-        <v>50.865760503876814</v>
+        <f t="shared" si="0"/>
+        <v>251.34402940917812</v>
       </c>
       <c r="BW13">
-        <f t="shared" si="1"/>
-        <v>50.357102898838043</v>
+        <f t="shared" si="0"/>
+        <v>248.83058911508633</v>
       </c>
       <c r="BX13">
-        <f t="shared" si="1"/>
-        <v>49.853531869849661</v>
+        <f t="shared" si="0"/>
+        <v>246.34228322393545</v>
       </c>
       <c r="BY13">
-        <f t="shared" si="1"/>
-        <v>49.354996551151167</v>
+        <f t="shared" si="0"/>
+        <v>243.87886039169609</v>
       </c>
       <c r="BZ13">
-        <f t="shared" si="1"/>
-        <v>48.861446585639655</v>
+        <f t="shared" si="0"/>
+        <v>241.44007178777912</v>
       </c>
       <c r="CA13">
-        <f t="shared" si="1"/>
-        <v>48.372832119783261</v>
+        <f t="shared" si="0"/>
+        <v>239.02567106990134</v>
       </c>
       <c r="CB13">
-        <f t="shared" si="1"/>
-        <v>47.889103798585431</v>
+        <f t="shared" si="0"/>
+        <v>236.63541435920231</v>
       </c>
       <c r="CC13">
-        <f t="shared" si="1"/>
-        <v>47.410212760599578</v>
+        <f t="shared" si="0"/>
+        <v>234.2690602156103</v>
       </c>
       <c r="CD13">
-        <f t="shared" ref="CD13:DU13" si="2">CC13*0.99</f>
-        <v>46.936110632993582</v>
+        <f t="shared" ref="CD13:DU13" si="1">CC13*(1+$O$31)</f>
+        <v>231.9263696134542</v>
       </c>
       <c r="CE13">
-        <f t="shared" si="2"/>
-        <v>46.466749526663648</v>
+        <f t="shared" si="1"/>
+        <v>229.60710591731964</v>
       </c>
       <c r="CF13">
-        <f t="shared" si="2"/>
-        <v>46.002082031397009</v>
+        <f t="shared" si="1"/>
+        <v>227.31103485814646</v>
       </c>
       <c r="CG13">
-        <f t="shared" si="2"/>
-        <v>45.542061211083038</v>
+        <f t="shared" si="1"/>
+        <v>225.03792450956499</v>
       </c>
       <c r="CH13">
-        <f t="shared" si="2"/>
-        <v>45.08664059897221</v>
+        <f t="shared" si="1"/>
+        <v>222.78754526446934</v>
       </c>
       <c r="CI13">
-        <f t="shared" si="2"/>
-        <v>44.635774192982488</v>
+        <f t="shared" si="1"/>
+        <v>220.55966981182465</v>
       </c>
       <c r="CJ13">
-        <f t="shared" si="2"/>
-        <v>44.189416451052665</v>
+        <f t="shared" si="1"/>
+        <v>218.35407311370639</v>
       </c>
       <c r="CK13">
-        <f t="shared" si="2"/>
-        <v>43.747522286542136</v>
+        <f t="shared" si="1"/>
+        <v>216.17053238256932</v>
       </c>
       <c r="CL13">
-        <f t="shared" si="2"/>
-        <v>43.310047063676713</v>
+        <f t="shared" si="1"/>
+        <v>214.00882705874363</v>
       </c>
       <c r="CM13">
-        <f t="shared" si="2"/>
-        <v>42.876946593039946</v>
+        <f t="shared" si="1"/>
+        <v>211.86873878815621</v>
       </c>
       <c r="CN13">
-        <f t="shared" si="2"/>
-        <v>42.448177127109545</v>
+        <f t="shared" si="1"/>
+        <v>209.75005140027466</v>
       </c>
       <c r="CO13">
-        <f t="shared" si="2"/>
-        <v>42.023695355838449</v>
+        <f t="shared" si="1"/>
+        <v>207.65255088627191</v>
       </c>
       <c r="CP13">
-        <f t="shared" si="2"/>
-        <v>41.603458402280062</v>
+        <f t="shared" si="1"/>
+        <v>205.5760253774092</v>
       </c>
       <c r="CQ13">
-        <f t="shared" si="2"/>
-        <v>41.187423818257258</v>
+        <f t="shared" si="1"/>
+        <v>203.52026512363511</v>
       </c>
       <c r="CR13">
-        <f t="shared" si="2"/>
-        <v>40.775549580074689</v>
+        <f t="shared" si="1"/>
+        <v>201.48506247239877</v>
       </c>
       <c r="CS13">
-        <f t="shared" si="2"/>
-        <v>40.367794084273939</v>
+        <f t="shared" si="1"/>
+        <v>199.47021184767479</v>
       </c>
       <c r="CT13">
-        <f t="shared" si="2"/>
-        <v>39.964116143431198</v>
+        <f t="shared" si="1"/>
+        <v>197.47550972919805</v>
       </c>
       <c r="CU13">
-        <f t="shared" si="2"/>
-        <v>39.564474981996888</v>
+        <f t="shared" si="1"/>
+        <v>195.50075463190606</v>
       </c>
       <c r="CV13">
-        <f t="shared" si="2"/>
-        <v>39.168830232176916</v>
+        <f t="shared" si="1"/>
+        <v>193.54574708558701</v>
       </c>
       <c r="CW13">
-        <f t="shared" si="2"/>
-        <v>38.777141929855148</v>
+        <f t="shared" si="1"/>
+        <v>191.61028961473113</v>
       </c>
       <c r="CX13">
-        <f t="shared" si="2"/>
-        <v>38.389370510556596</v>
+        <f t="shared" si="1"/>
+        <v>189.69418671858381</v>
       </c>
       <c r="CY13">
-        <f t="shared" si="2"/>
-        <v>38.005476805451032</v>
+        <f t="shared" si="1"/>
+        <v>187.79724485139798</v>
       </c>
       <c r="CZ13">
-        <f t="shared" si="2"/>
-        <v>37.625422037396518</v>
+        <f t="shared" si="1"/>
+        <v>185.91927240288399</v>
       </c>
       <c r="DA13">
-        <f t="shared" si="2"/>
-        <v>37.249167817022553</v>
+        <f t="shared" si="1"/>
+        <v>184.06007967885515</v>
       </c>
       <c r="DB13">
-        <f t="shared" si="2"/>
-        <v>36.876676138852325</v>
+        <f t="shared" si="1"/>
+        <v>182.2194788820666</v>
       </c>
       <c r="DC13">
-        <f t="shared" si="2"/>
-        <v>36.507909377463804</v>
+        <f t="shared" si="1"/>
+        <v>180.39728409324593</v>
       </c>
       <c r="DD13">
-        <f t="shared" si="2"/>
-        <v>36.142830283689165</v>
+        <f t="shared" si="1"/>
+        <v>178.59331125231347</v>
       </c>
       <c r="DE13">
-        <f t="shared" si="2"/>
-        <v>35.781401980852273</v>
+        <f t="shared" si="1"/>
+        <v>176.80737813979033</v>
       </c>
       <c r="DF13">
-        <f t="shared" si="2"/>
-        <v>35.423587961043751</v>
+        <f t="shared" si="1"/>
+        <v>175.03930435839243</v>
       </c>
       <c r="DG13">
-        <f t="shared" si="2"/>
-        <v>35.069352081433316</v>
+        <f t="shared" si="1"/>
+        <v>173.2889113148085</v>
       </c>
       <c r="DH13">
-        <f t="shared" si="2"/>
-        <v>34.718658560618984</v>
+        <f t="shared" si="1"/>
+        <v>171.55602220166043</v>
       </c>
       <c r="DI13">
-        <f t="shared" si="2"/>
-        <v>34.371471975012795</v>
+        <f t="shared" si="1"/>
+        <v>169.84046197964383</v>
       </c>
       <c r="DJ13">
-        <f t="shared" si="2"/>
-        <v>34.027757255262664</v>
+        <f t="shared" si="1"/>
+        <v>168.1420573598474</v>
       </c>
       <c r="DK13">
-        <f t="shared" si="2"/>
-        <v>33.687479682710034</v>
+        <f t="shared" si="1"/>
+        <v>166.46063678624893</v>
       </c>
       <c r="DL13">
-        <f t="shared" si="2"/>
-        <v>33.35060488588293</v>
+        <f t="shared" si="1"/>
+        <v>164.79603041838644</v>
       </c>
       <c r="DM13">
-        <f t="shared" si="2"/>
-        <v>33.017098837024101</v>
+        <f t="shared" si="1"/>
+        <v>163.14807011420257</v>
       </c>
       <c r="DN13">
-        <f t="shared" si="2"/>
-        <v>32.686927848653859</v>
+        <f t="shared" si="1"/>
+        <v>161.51658941306053</v>
       </c>
       <c r="DO13">
-        <f t="shared" si="2"/>
-        <v>32.360058570167318</v>
+        <f t="shared" si="1"/>
+        <v>159.90142351892993</v>
       </c>
       <c r="DP13">
-        <f t="shared" si="2"/>
-        <v>32.036457984465642</v>
+        <f t="shared" si="1"/>
+        <v>158.30240928374064</v>
       </c>
       <c r="DQ13">
-        <f t="shared" si="2"/>
-        <v>31.716093404620985</v>
+        <f t="shared" si="1"/>
+        <v>156.71938519090324</v>
       </c>
       <c r="DR13">
-        <f t="shared" si="2"/>
-        <v>31.398932470574774</v>
+        <f t="shared" si="1"/>
+        <v>155.15219133899421</v>
       </c>
       <c r="DS13">
-        <f t="shared" si="2"/>
-        <v>31.084943145869026</v>
+        <f t="shared" si="1"/>
+        <v>153.60066942560428</v>
       </c>
       <c r="DT13">
-        <f t="shared" si="2"/>
-        <v>30.774093714410334</v>
+        <f t="shared" si="1"/>
+        <v>152.06466273134825</v>
       </c>
       <c r="DU13">
-        <f t="shared" si="2"/>
-        <v>30.466352777266231</v>
+        <f t="shared" si="1"/>
+        <v>150.54401610403477</v>
       </c>
     </row>
     <row r="14" spans="1:125" x14ac:dyDescent="0.25">
@@ -1426,8 +1678,13 @@
         <f>I13/I15</f>
         <v>0.15851514838175995</v>
       </c>
-      <c r="M14">
-        <v>0</v>
+      <c r="J14" s="4">
+        <f>J13/J15</f>
+        <v>8.4790673025967087E-2</v>
+      </c>
+      <c r="K14" s="4">
+        <f>K13/K15</f>
+        <v>0.11811821960863825</v>
       </c>
     </row>
     <row r="15" spans="1:125" x14ac:dyDescent="0.25">
@@ -1437,13 +1694,14 @@
       <c r="I15" s="4">
         <v>193.42</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="N17" t="s">
-        <v>26</v>
-      </c>
-      <c r="O17" s="5">
-        <v>7.0000000000000007E-2</v>
+      <c r="J15">
+        <v>188.7</v>
+      </c>
+      <c r="K15">
+        <v>197.26</v>
+      </c>
+      <c r="L15">
+        <v>198.7</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -1466,13 +1724,17 @@
         <f>I3/H3-1</f>
         <v>0.41488342382625354</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="N18" t="s">
-        <v>27</v>
-      </c>
-      <c r="O18" s="6">
-        <f>NPV(O17,J13:DU13)</f>
-        <v>992.47056565316029</v>
+      <c r="J18" s="3">
+        <f>J3/I3-1</f>
+        <v>-2.3702031602708895E-2</v>
+      </c>
+      <c r="K18" s="3">
+        <f>K3/J3-1</f>
+        <v>0.24547206165703273</v>
+      </c>
+      <c r="L18" s="3">
+        <f>L3/K3-1</f>
+        <v>0.66921410891089117</v>
       </c>
     </row>
     <row r="19" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1499,12 +1761,17 @@
         <f>I5/I3</f>
         <v>0.24815650865312266</v>
       </c>
-      <c r="N19" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O19" s="1">
-        <f>O18/I15</f>
-        <v>5.1311682641565524</v>
+      <c r="J19" s="3">
+        <f>J5/J3</f>
+        <v>0.24354527938342962</v>
+      </c>
+      <c r="K19" s="3">
+        <f>K5/K3</f>
+        <v>0.24071782178217818</v>
+      </c>
+      <c r="L19" s="3">
+        <f>L5/L3</f>
+        <v>0.23121837290774622</v>
       </c>
     </row>
     <row r="20" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1516,20 +1783,32 @@
         <v>0.13102751830345871</v>
       </c>
       <c r="F20" s="3">
-        <f t="shared" ref="F20:I20" si="3">F9/F3</f>
+        <f t="shared" ref="F20:I20" si="2">F9/F3</f>
         <v>0.20676541232986384</v>
       </c>
       <c r="G20" s="3">
+        <f t="shared" si="2"/>
+        <v>0.14894373710790243</v>
+      </c>
+      <c r="H20" s="3">
+        <f t="shared" si="2"/>
+        <v>0.11364846162035558</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="2"/>
+        <v>0.14202407825432659</v>
+      </c>
+      <c r="J20" s="3">
+        <f t="shared" ref="J20:K20" si="3">J9/J3</f>
+        <v>7.8998073217726339E-2</v>
+      </c>
+      <c r="K20" s="3">
         <f t="shared" si="3"/>
-        <v>0.14894373710790243</v>
-      </c>
-      <c r="H20" s="3">
-        <f t="shared" si="3"/>
-        <v>0.11364846162035558</v>
-      </c>
-      <c r="I20" s="3">
-        <f t="shared" si="3"/>
-        <v>0.14202407825432659</v>
+        <v>8.5705445544554407E-2</v>
+      </c>
+      <c r="L20" s="3">
+        <f t="shared" ref="L20" si="4">L9/L3</f>
+        <v>8.4413056775843862E-2</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -1556,10 +1835,22 @@
         <f>I12/I11</f>
         <v>0.17757510729613729</v>
       </c>
+      <c r="J21" s="3">
+        <f>J12/J11</f>
+        <v>0.22330097087378653</v>
+      </c>
+      <c r="K21" s="3">
+        <f>K12/K11</f>
+        <v>0.17081850533807841</v>
+      </c>
+      <c r="L21" s="3">
+        <f>L12/L11</f>
+        <v>0.10883761427949498</v>
+      </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E22" s="3">
         <f>E13/E3</f>
@@ -1581,6 +1872,18 @@
         <f>I13/I3</f>
         <v>0.11534988713318287</v>
       </c>
+      <c r="J22" s="3">
+        <f>J13/J3</f>
+        <v>6.1657032755298602E-2</v>
+      </c>
+      <c r="K22" s="3">
+        <f>K13/K3</f>
+        <v>7.2091584158415781E-2</v>
+      </c>
+      <c r="L22" s="3">
+        <f>L13/L3</f>
+        <v>7.5886485384344476E-2</v>
+      </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
@@ -1599,7 +1902,13 @@
         <v>14.34</v>
       </c>
       <c r="I24">
-        <v>16.489999999999998</v>
+        <v>21.1</v>
+      </c>
+      <c r="J24">
+        <v>-3.2</v>
+      </c>
+      <c r="K24">
+        <v>6.2</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -1621,6 +1930,12 @@
       <c r="I25">
         <v>-3.88</v>
       </c>
+      <c r="J25">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="K25">
+        <v>-1.8</v>
+      </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
@@ -1644,11 +1959,77 @@
       </c>
       <c r="I26">
         <f>SUM(I24:I25)</f>
-        <v>12.61</v>
+        <v>17.220000000000002</v>
+      </c>
+      <c r="J26">
+        <f>SUM(J24:J25)</f>
+        <v>-5.4</v>
+      </c>
+      <c r="K26">
+        <f>SUM(K24:K25)</f>
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G28" s="2">
+        <v>40.58</v>
+      </c>
+      <c r="H28" s="2">
+        <v>47.89</v>
+      </c>
+      <c r="I28" s="2">
+        <v>108.1</v>
+      </c>
+      <c r="J28" s="2">
+        <v>156.69999999999999</v>
+      </c>
+      <c r="K28" s="2">
+        <v>145.30000000000001</v>
+      </c>
+      <c r="L28" s="2">
+        <v>262.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N31" t="s">
+        <v>31</v>
+      </c>
+      <c r="O31" s="3">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N32" t="s">
+        <v>25</v>
+      </c>
+      <c r="O32" s="5">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="33" spans="14:15" x14ac:dyDescent="0.25">
+      <c r="N33" t="s">
+        <v>26</v>
+      </c>
+      <c r="O33" s="6">
+        <f>NPV(O32,J13:DU13)</f>
+        <v>2675.5300746330786</v>
+      </c>
+    </row>
+    <row r="34" spans="14:15" x14ac:dyDescent="0.25">
+      <c r="N34" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O34" s="1">
+        <f>O33/I15</f>
+        <v>13.832747774961632</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/RPI.xlsx
+++ b/RPI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2001s\modele\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB2B437-E31D-4A86-B91E-A6BFDBED1E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1EC8E80-A668-496B-98DD-2F51BD3890A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{E98EB17B-F02A-46E8-ACDF-C760F78E9737}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="15285" activeTab="1" xr2:uid="{E98EB17B-F02A-46E8-ACDF-C760F78E9737}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>Price</t>
   </si>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t>terminal value</t>
+  </si>
+  <si>
+    <t>upside</t>
   </si>
 </sst>
 </file>
@@ -143,7 +146,7 @@
     <numFmt numFmtId="164" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,6 +157,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -181,17 +191,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -644,12 +657,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E15DC23F-DC20-407B-BB0E-87053752C463}">
-  <dimension ref="A2:DU34"/>
+  <dimension ref="A2:DU35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="0" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -678,16 +691,16 @@
       <c r="L2">
         <v>2026</v>
       </c>
-      <c r="M2" s="9">
+      <c r="M2" s="7">
         <v>2027</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="7">
         <v>2028</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="7">
         <v>2029</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="7">
         <v>2030</v>
       </c>
     </row>
@@ -720,19 +733,19 @@
         <f>256.9*2.1</f>
         <v>539.49</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3" s="5">
         <f>L3*1.6</f>
         <v>863.18400000000008</v>
       </c>
-      <c r="N3" s="7">
+      <c r="N3" s="5">
         <f>M3*1.6</f>
         <v>1381.0944000000002</v>
       </c>
-      <c r="O3" s="7">
+      <c r="O3" s="5">
         <f>N3*1.6</f>
         <v>2209.7510400000006</v>
       </c>
-      <c r="P3" s="7">
+      <c r="P3" s="5">
         <f>O3*1.6</f>
         <v>3535.6016640000012</v>
       </c>
@@ -788,51 +801,51 @@
         <v>9</v>
       </c>
       <c r="E5">
-        <f>E3-E4</f>
+        <f t="shared" ref="E5:P5" si="0">E3-E4</f>
         <v>16.309999999999999</v>
       </c>
       <c r="F5">
-        <f>F3-F4</f>
+        <f t="shared" si="0"/>
         <v>30.409999999999997</v>
       </c>
       <c r="G5">
-        <f>G3-G4</f>
+        <f t="shared" si="0"/>
         <v>41.92</v>
       </c>
       <c r="H5">
-        <f>H3-H4</f>
+        <f t="shared" si="0"/>
         <v>42.28</v>
       </c>
       <c r="I5">
-        <f>I3-I4</f>
+        <f t="shared" si="0"/>
         <v>65.960000000000008</v>
       </c>
       <c r="J5">
-        <f>J3-J4</f>
+        <f t="shared" si="0"/>
         <v>63.199999999999989</v>
       </c>
       <c r="K5">
-        <f>K3-K4</f>
+        <f t="shared" si="0"/>
         <v>77.799999999999983</v>
       </c>
       <c r="L5">
-        <f>L3-L4</f>
+        <f t="shared" si="0"/>
         <v>124.74000000000001</v>
       </c>
       <c r="M5" s="4">
-        <f>M3-M4</f>
+        <f t="shared" si="0"/>
         <v>207.16416000000004</v>
       </c>
       <c r="N5" s="4">
-        <f>N3-N4</f>
+        <f t="shared" si="0"/>
         <v>331.46265599999992</v>
       </c>
       <c r="O5" s="4">
-        <f>O3-O4</f>
+        <f t="shared" si="0"/>
         <v>530.34024960000011</v>
       </c>
       <c r="P5" s="4">
-        <f>P3-P4</f>
+        <f t="shared" si="0"/>
         <v>848.54439936000017</v>
       </c>
     </row>
@@ -931,51 +944,51 @@
         <v>13</v>
       </c>
       <c r="E8">
-        <f>SUM(E6:E7)</f>
+        <f t="shared" ref="E8:P8" si="1">SUM(E6:E7)</f>
         <v>11.12</v>
       </c>
       <c r="F8">
-        <f>SUM(F6:F7)</f>
+        <f t="shared" si="1"/>
         <v>9.75</v>
       </c>
       <c r="G8">
-        <f>SUM(G6:G7)</f>
+        <f t="shared" si="1"/>
         <v>20.979999999999997</v>
       </c>
       <c r="H8">
-        <f>SUM(H6:H7)</f>
+        <f t="shared" si="1"/>
         <v>20.93</v>
       </c>
       <c r="I8">
-        <f>SUM(I6:I7)</f>
+        <f t="shared" si="1"/>
         <v>28.21</v>
       </c>
       <c r="J8">
-        <f>SUM(J6:J7)</f>
+        <f t="shared" si="1"/>
         <v>42.7</v>
       </c>
       <c r="K8">
-        <f>SUM(K6:K7)</f>
+        <f t="shared" si="1"/>
         <v>50.1</v>
       </c>
       <c r="L8">
-        <f>SUM(L6:L7)</f>
+        <f t="shared" si="1"/>
         <v>79.2</v>
       </c>
       <c r="M8" s="4">
-        <f>SUM(M6:M7)</f>
+        <f t="shared" si="1"/>
         <v>108.32</v>
       </c>
       <c r="N8" s="4">
-        <f>SUM(N6:N7)</f>
+        <f t="shared" si="1"/>
         <v>151.23200000000003</v>
       </c>
       <c r="O8" s="4">
-        <f>SUM(O6:O7)</f>
+        <f t="shared" si="1"/>
         <v>215.47520000000003</v>
       </c>
       <c r="P8" s="4">
-        <f>SUM(P6:P7)</f>
+        <f t="shared" si="1"/>
         <v>312.96512000000007</v>
       </c>
     </row>
@@ -984,51 +997,51 @@
         <v>14</v>
       </c>
       <c r="E9">
-        <f>E5-E8</f>
+        <f t="shared" ref="E9:P9" si="2">E5-E8</f>
         <v>5.1899999999999995</v>
       </c>
       <c r="F9">
-        <f>F5-F8</f>
+        <f t="shared" si="2"/>
         <v>20.659999999999997</v>
       </c>
       <c r="G9">
-        <f>G5-G8</f>
+        <f t="shared" si="2"/>
         <v>20.940000000000005</v>
       </c>
       <c r="H9">
-        <f>H5-H8</f>
+        <f t="shared" si="2"/>
         <v>21.35</v>
       </c>
       <c r="I9">
-        <f>I5-I8</f>
+        <f t="shared" si="2"/>
         <v>37.750000000000007</v>
       </c>
       <c r="J9">
-        <f>J5-J8</f>
+        <f t="shared" si="2"/>
         <v>20.499999999999986</v>
       </c>
       <c r="K9">
-        <f>K5-K8</f>
+        <f t="shared" si="2"/>
         <v>27.699999999999982</v>
       </c>
       <c r="L9">
-        <f>L5-L8</f>
+        <f t="shared" si="2"/>
         <v>45.540000000000006</v>
       </c>
       <c r="M9" s="4">
-        <f>M5-M8</f>
+        <f t="shared" si="2"/>
         <v>98.844160000000045</v>
       </c>
       <c r="N9" s="4">
-        <f>N5-N8</f>
+        <f t="shared" si="2"/>
         <v>180.2306559999999</v>
       </c>
       <c r="O9" s="4">
-        <f>O5-O8</f>
+        <f t="shared" si="2"/>
         <v>314.86504960000008</v>
       </c>
       <c r="P9" s="4">
-        <f>P5-P8</f>
+        <f t="shared" si="2"/>
         <v>535.5792793600001</v>
       </c>
     </row>
@@ -1062,23 +1075,23 @@
         <f>1-1.4</f>
         <v>-0.39999999999999991</v>
       </c>
-      <c r="L10" s="8">
+      <c r="L10" s="6">
         <f>-0.4</f>
         <v>-0.4</v>
       </c>
-      <c r="M10" s="8">
+      <c r="M10" s="6">
         <f>-0.4</f>
         <v>-0.4</v>
       </c>
-      <c r="N10" s="8">
+      <c r="N10" s="6">
         <f>-0.4</f>
         <v>-0.4</v>
       </c>
-      <c r="O10" s="8">
+      <c r="O10" s="6">
         <f>-0.4</f>
         <v>-0.4</v>
       </c>
-      <c r="P10" s="8">
+      <c r="P10" s="6">
         <f>-0.4</f>
         <v>-0.4</v>
       </c>
@@ -1088,51 +1101,51 @@
         <v>17</v>
       </c>
       <c r="E11">
-        <f>E9-E10</f>
+        <f t="shared" ref="E11:P11" si="3">E9-E10</f>
         <v>5.1899999999999995</v>
       </c>
       <c r="F11">
-        <f>F9-F10</f>
+        <f t="shared" si="3"/>
         <v>20.789999999999996</v>
       </c>
       <c r="G11">
-        <f>G9-G10</f>
+        <f t="shared" si="3"/>
         <v>21.510000000000005</v>
       </c>
       <c r="H11">
-        <f>H9-H10</f>
+        <f t="shared" si="3"/>
         <v>20.5</v>
       </c>
       <c r="I11">
-        <f>I9-I10</f>
+        <f t="shared" si="3"/>
         <v>37.280000000000008</v>
       </c>
       <c r="J11">
-        <f>J9-J10</f>
+        <f t="shared" si="3"/>
         <v>20.599999999999987</v>
       </c>
       <c r="K11">
-        <f>K9-K10</f>
+        <f t="shared" si="3"/>
         <v>28.09999999999998</v>
       </c>
       <c r="L11" s="4">
-        <f>L9-L10</f>
+        <f t="shared" si="3"/>
         <v>45.940000000000005</v>
       </c>
       <c r="M11" s="4">
-        <f>M9-M10</f>
+        <f t="shared" si="3"/>
         <v>99.244160000000051</v>
       </c>
       <c r="N11" s="4">
-        <f>N9-N10</f>
+        <f t="shared" si="3"/>
         <v>180.6306559999999</v>
       </c>
       <c r="O11" s="4">
-        <f>O9-O10</f>
+        <f t="shared" si="3"/>
         <v>315.26504960000005</v>
       </c>
       <c r="P11" s="4">
-        <f>P9-P10</f>
+        <f t="shared" si="3"/>
         <v>535.97927936000008</v>
       </c>
     </row>
@@ -1186,51 +1199,51 @@
         <v>19</v>
       </c>
       <c r="E13">
-        <f>E11-E12</f>
+        <f t="shared" ref="E13:P13" si="4">E11-E12</f>
         <v>5.1899999999999995</v>
       </c>
       <c r="F13">
-        <f>F11-F12</f>
+        <f t="shared" si="4"/>
         <v>19.649999999999995</v>
       </c>
       <c r="G13">
-        <f>G11-G12</f>
+        <f t="shared" si="4"/>
         <v>17.890000000000004</v>
       </c>
       <c r="H13">
-        <f>H11-H12</f>
+        <f t="shared" si="4"/>
         <v>17.48</v>
       </c>
       <c r="I13">
-        <f>I11-I12</f>
+        <f t="shared" si="4"/>
         <v>30.660000000000007</v>
       </c>
       <c r="J13">
-        <f>J11-J12</f>
+        <f t="shared" si="4"/>
         <v>15.999999999999988</v>
       </c>
       <c r="K13">
-        <f>K11-K12</f>
+        <f t="shared" si="4"/>
         <v>23.299999999999979</v>
       </c>
       <c r="L13" s="4">
-        <f>L11-L12</f>
+        <f t="shared" si="4"/>
         <v>40.940000000000005</v>
       </c>
       <c r="M13" s="4">
-        <f>M11-M12</f>
+        <f t="shared" si="4"/>
         <v>83.365094400000046</v>
       </c>
       <c r="N13" s="4">
-        <f>N11-N12</f>
+        <f t="shared" si="4"/>
         <v>151.72975103999991</v>
       </c>
       <c r="O13" s="4">
-        <f>O11-O12</f>
+        <f t="shared" si="4"/>
         <v>264.82264166400006</v>
       </c>
       <c r="P13" s="4">
-        <f>P11-P12</f>
+        <f t="shared" si="4"/>
         <v>450.22259466240007</v>
       </c>
       <c r="Q13">
@@ -1238,435 +1251,435 @@
         <v>445.72036871577609</v>
       </c>
       <c r="R13">
-        <f t="shared" ref="R13:CC13" si="0">Q13*(1+$O$31)</f>
+        <f t="shared" ref="R13:CC13" si="5">Q13*(1+$O$31)</f>
         <v>441.26316502861835</v>
       </c>
       <c r="S13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>436.85053337833216</v>
       </c>
       <c r="T13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>432.48202804454883</v>
       </c>
       <c r="U13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>428.15720776410336</v>
       </c>
       <c r="V13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>423.87563568646232</v>
       </c>
       <c r="W13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>419.63687932959772</v>
       </c>
       <c r="X13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>415.44051053630176</v>
       </c>
       <c r="Y13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>411.28610543093873</v>
       </c>
       <c r="Z13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>407.17324437662933</v>
       </c>
       <c r="AA13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>403.10151193286305</v>
       </c>
       <c r="AB13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>399.07049681353442</v>
       </c>
       <c r="AC13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>395.07979184539909</v>
       </c>
       <c r="AD13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>391.1289939269451</v>
       </c>
       <c r="AE13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>387.21770398767563</v>
       </c>
       <c r="AF13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>383.34552694779887</v>
       </c>
       <c r="AG13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>379.51207167832086</v>
       </c>
       <c r="AH13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>375.71695096153763</v>
       </c>
       <c r="AI13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>371.95978145192225</v>
       </c>
       <c r="AJ13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>368.24018363740305</v>
       </c>
       <c r="AK13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>364.55778180102902</v>
       </c>
       <c r="AL13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>360.91220398301874</v>
       </c>
       <c r="AM13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>357.30308194318854</v>
       </c>
       <c r="AN13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>353.73005112375665</v>
       </c>
       <c r="AO13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>350.19275061251909</v>
       </c>
       <c r="AP13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>346.69082310639391</v>
       </c>
       <c r="AQ13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>343.22391487532997</v>
       </c>
       <c r="AR13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>339.79167572657667</v>
       </c>
       <c r="AS13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>336.39375896931091</v>
       </c>
       <c r="AT13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>333.02982137961777</v>
       </c>
       <c r="AU13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>329.69952316582157</v>
       </c>
       <c r="AV13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>326.40252793416334</v>
       </c>
       <c r="AW13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>323.13850265482171</v>
       </c>
       <c r="AX13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>319.90711762827351</v>
       </c>
       <c r="AY13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>316.70804645199075</v>
       </c>
       <c r="AZ13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>313.54096598747083</v>
       </c>
       <c r="BA13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>310.40555632759612</v>
       </c>
       <c r="BB13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>307.30150076432017</v>
       </c>
       <c r="BC13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>304.22848575667695</v>
       </c>
       <c r="BD13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>301.18620089911019</v>
       </c>
       <c r="BE13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>298.17433889011909</v>
       </c>
       <c r="BF13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>295.19259550121791</v>
       </c>
       <c r="BG13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>292.24066954620571</v>
       </c>
       <c r="BH13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>289.31826285074362</v>
       </c>
       <c r="BI13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>286.4250802222362</v>
       </c>
       <c r="BJ13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>283.56082942001382</v>
       </c>
       <c r="BK13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>280.72522112581368</v>
       </c>
       <c r="BL13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>277.91796891455556</v>
       </c>
       <c r="BM13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>275.13878922540999</v>
       </c>
       <c r="BN13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>272.38740133315588</v>
       </c>
       <c r="BO13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>269.66352731982431</v>
       </c>
       <c r="BP13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>266.96689204662607</v>
       </c>
       <c r="BQ13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>264.29722312615979</v>
       </c>
       <c r="BR13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>261.65425089489821</v>
       </c>
       <c r="BS13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>259.0377083859492</v>
       </c>
       <c r="BT13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>256.44733130208971</v>
       </c>
       <c r="BU13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>253.88285798906881</v>
       </c>
       <c r="BV13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>251.34402940917812</v>
       </c>
       <c r="BW13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>248.83058911508633</v>
       </c>
       <c r="BX13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>246.34228322393545</v>
       </c>
       <c r="BY13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>243.87886039169609</v>
       </c>
       <c r="BZ13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>241.44007178777912</v>
       </c>
       <c r="CA13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>239.02567106990134</v>
       </c>
       <c r="CB13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>236.63541435920231</v>
       </c>
       <c r="CC13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>234.2690602156103</v>
       </c>
       <c r="CD13">
-        <f t="shared" ref="CD13:DU13" si="1">CC13*(1+$O$31)</f>
+        <f t="shared" ref="CD13:DU13" si="6">CC13*(1+$O$31)</f>
         <v>231.9263696134542</v>
       </c>
       <c r="CE13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>229.60710591731964</v>
       </c>
       <c r="CF13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>227.31103485814646</v>
       </c>
       <c r="CG13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>225.03792450956499</v>
       </c>
       <c r="CH13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>222.78754526446934</v>
       </c>
       <c r="CI13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>220.55966981182465</v>
       </c>
       <c r="CJ13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>218.35407311370639</v>
       </c>
       <c r="CK13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>216.17053238256932</v>
       </c>
       <c r="CL13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>214.00882705874363</v>
       </c>
       <c r="CM13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>211.86873878815621</v>
       </c>
       <c r="CN13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>209.75005140027466</v>
       </c>
       <c r="CO13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>207.65255088627191</v>
       </c>
       <c r="CP13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>205.5760253774092</v>
       </c>
       <c r="CQ13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>203.52026512363511</v>
       </c>
       <c r="CR13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>201.48506247239877</v>
       </c>
       <c r="CS13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>199.47021184767479</v>
       </c>
       <c r="CT13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>197.47550972919805</v>
       </c>
       <c r="CU13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>195.50075463190606</v>
       </c>
       <c r="CV13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>193.54574708558701</v>
       </c>
       <c r="CW13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>191.61028961473113</v>
       </c>
       <c r="CX13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>189.69418671858381</v>
       </c>
       <c r="CY13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>187.79724485139798</v>
       </c>
       <c r="CZ13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>185.91927240288399</v>
       </c>
       <c r="DA13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>184.06007967885515</v>
       </c>
       <c r="DB13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>182.2194788820666</v>
       </c>
       <c r="DC13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>180.39728409324593</v>
       </c>
       <c r="DD13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>178.59331125231347</v>
       </c>
       <c r="DE13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>176.80737813979033</v>
       </c>
       <c r="DF13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>175.03930435839243</v>
       </c>
       <c r="DG13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>173.2889113148085</v>
       </c>
       <c r="DH13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>171.55602220166043</v>
       </c>
       <c r="DI13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>169.84046197964383</v>
       </c>
       <c r="DJ13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>168.1420573598474</v>
       </c>
       <c r="DK13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>166.46063678624893</v>
       </c>
       <c r="DL13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>164.79603041838644</v>
       </c>
       <c r="DM13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>163.14807011420257</v>
       </c>
       <c r="DN13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>161.51658941306053</v>
       </c>
       <c r="DO13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>159.90142351892993</v>
       </c>
       <c r="DP13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>158.30240928374064</v>
       </c>
       <c r="DQ13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>156.71938519090324</v>
       </c>
       <c r="DR13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>155.15219133899421</v>
       </c>
       <c r="DS13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>153.60066942560428</v>
       </c>
       <c r="DT13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>152.06466273134825</v>
       </c>
       <c r="DU13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>150.54401610403477</v>
       </c>
     </row>
@@ -1709,31 +1722,31 @@
         <v>7</v>
       </c>
       <c r="F18" s="3">
-        <f>F3/E3-1</f>
+        <f t="shared" ref="F18:L18" si="7">F3/E3-1</f>
         <v>1.5225953042161073</v>
       </c>
       <c r="G18" s="3">
-        <f>G3/F3-1</f>
+        <f t="shared" si="7"/>
         <v>0.40702562049639712</v>
       </c>
       <c r="H18" s="3">
-        <f>H3/G3-1</f>
+        <f t="shared" si="7"/>
         <v>0.33622590511416184</v>
       </c>
       <c r="I18" s="3">
-        <f>I3/H3-1</f>
+        <f t="shared" si="7"/>
         <v>0.41488342382625354</v>
       </c>
       <c r="J18" s="3">
-        <f>J3/I3-1</f>
+        <f t="shared" si="7"/>
         <v>-2.3702031602708895E-2</v>
       </c>
       <c r="K18" s="3">
-        <f>K3/J3-1</f>
+        <f t="shared" si="7"/>
         <v>0.24547206165703273</v>
       </c>
       <c r="L18" s="3">
-        <f>L3/K3-1</f>
+        <f t="shared" si="7"/>
         <v>0.66921410891089117</v>
       </c>
     </row>
@@ -1742,35 +1755,35 @@
         <v>10</v>
       </c>
       <c r="E19" s="3">
-        <f>E5/E3</f>
+        <f t="shared" ref="E19:L19" si="8">E5/E3</f>
         <v>0.41176470588235292</v>
       </c>
       <c r="F19" s="3">
-        <f>F5/F3</f>
+        <f t="shared" si="8"/>
         <v>0.30434347477982382</v>
       </c>
       <c r="G19" s="3">
-        <f>G5/G3</f>
+        <f t="shared" si="8"/>
         <v>0.29817198947293549</v>
       </c>
       <c r="H19" s="3">
-        <f>H5/H3</f>
+        <f t="shared" si="8"/>
         <v>0.22506121579899924</v>
       </c>
       <c r="I19" s="3">
-        <f>I5/I3</f>
+        <f t="shared" si="8"/>
         <v>0.24815650865312266</v>
       </c>
       <c r="J19" s="3">
-        <f>J5/J3</f>
+        <f t="shared" si="8"/>
         <v>0.24354527938342962</v>
       </c>
       <c r="K19" s="3">
-        <f>K5/K3</f>
+        <f t="shared" si="8"/>
         <v>0.24071782178217818</v>
       </c>
       <c r="L19" s="3">
-        <f>L5/L3</f>
+        <f t="shared" si="8"/>
         <v>0.23121837290774622</v>
       </c>
     </row>
@@ -1783,31 +1796,31 @@
         <v>0.13102751830345871</v>
       </c>
       <c r="F20" s="3">
-        <f t="shared" ref="F20:I20" si="2">F9/F3</f>
+        <f t="shared" ref="F20:I20" si="9">F9/F3</f>
         <v>0.20676541232986384</v>
       </c>
       <c r="G20" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>0.14894373710790243</v>
       </c>
       <c r="H20" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>0.11364846162035558</v>
       </c>
       <c r="I20" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>0.14202407825432659</v>
       </c>
       <c r="J20" s="3">
-        <f t="shared" ref="J20:K20" si="3">J9/J3</f>
+        <f t="shared" ref="J20:K20" si="10">J9/J3</f>
         <v>7.8998073217726339E-2</v>
       </c>
       <c r="K20" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>8.5705445544554407E-2</v>
       </c>
       <c r="L20" s="3">
-        <f t="shared" ref="L20" si="4">L9/L3</f>
+        <f t="shared" ref="L20" si="11">L9/L3</f>
         <v>8.4413056775843862E-2</v>
       </c>
     </row>
@@ -1816,35 +1829,35 @@
         <v>21</v>
       </c>
       <c r="E21" s="3">
-        <f>E12/E11</f>
+        <f t="shared" ref="E21:L21" si="12">E12/E11</f>
         <v>0</v>
       </c>
       <c r="F21" s="3">
-        <f>F12/F11</f>
+        <f t="shared" si="12"/>
         <v>5.4834054834054839E-2</v>
       </c>
       <c r="G21" s="3">
-        <f>G12/G11</f>
+        <f t="shared" si="12"/>
         <v>0.16829381682938166</v>
       </c>
       <c r="H21" s="3">
-        <f>H12/H11</f>
+        <f t="shared" si="12"/>
         <v>0.1473170731707317</v>
       </c>
       <c r="I21" s="3">
-        <f>I12/I11</f>
+        <f t="shared" si="12"/>
         <v>0.17757510729613729</v>
       </c>
       <c r="J21" s="3">
-        <f>J12/J11</f>
+        <f t="shared" si="12"/>
         <v>0.22330097087378653</v>
       </c>
       <c r="K21" s="3">
-        <f>K12/K11</f>
+        <f t="shared" si="12"/>
         <v>0.17081850533807841</v>
       </c>
       <c r="L21" s="3">
-        <f>L12/L11</f>
+        <f t="shared" si="12"/>
         <v>0.10883761427949498</v>
       </c>
     </row>
@@ -1853,35 +1866,35 @@
         <v>28</v>
       </c>
       <c r="E22" s="3">
-        <f>E13/E3</f>
+        <f t="shared" ref="E22:L22" si="13">E13/E3</f>
         <v>0.13102751830345871</v>
       </c>
       <c r="F22" s="3">
-        <f>F13/F3</f>
+        <f t="shared" si="13"/>
         <v>0.19665732586068849</v>
       </c>
       <c r="G22" s="3">
-        <f>G13/G3</f>
+        <f t="shared" si="13"/>
         <v>0.12724944875168934</v>
       </c>
       <c r="H22" s="3">
-        <f>H13/H3</f>
+        <f t="shared" si="13"/>
         <v>9.3048014478867236E-2</v>
       </c>
       <c r="I22" s="3">
-        <f>I13/I3</f>
+        <f t="shared" si="13"/>
         <v>0.11534988713318287</v>
       </c>
       <c r="J22" s="3">
-        <f>J13/J3</f>
+        <f t="shared" si="13"/>
         <v>6.1657032755298602E-2</v>
       </c>
       <c r="K22" s="3">
-        <f>K13/K3</f>
+        <f t="shared" si="13"/>
         <v>7.2091584158415781E-2</v>
       </c>
       <c r="L22" s="3">
-        <f>L13/L3</f>
+        <f t="shared" si="13"/>
         <v>7.5886485384344476E-2</v>
       </c>
     </row>
@@ -1942,31 +1955,31 @@
         <v>24</v>
       </c>
       <c r="E26">
-        <f>SUM(E24:E25)</f>
+        <f t="shared" ref="E26:K26" si="14">SUM(E24:E25)</f>
         <v>8.44</v>
       </c>
       <c r="F26">
-        <f>SUM(F24:F25)</f>
+        <f t="shared" si="14"/>
         <v>9.19</v>
       </c>
       <c r="G26">
-        <f>SUM(G24:G25)</f>
+        <f t="shared" si="14"/>
         <v>-2.29</v>
       </c>
       <c r="H26">
-        <f>SUM(H24:H25)</f>
+        <f t="shared" si="14"/>
         <v>12.2</v>
       </c>
       <c r="I26">
-        <f>SUM(I24:I25)</f>
+        <f t="shared" si="14"/>
         <v>17.220000000000002</v>
       </c>
       <c r="J26">
-        <f>SUM(J24:J25)</f>
+        <f t="shared" si="14"/>
         <v>-5.4</v>
       </c>
       <c r="K26">
-        <f>SUM(K24:K25)</f>
+        <f t="shared" si="14"/>
         <v>4.4000000000000004</v>
       </c>
     </row>
@@ -1993,38 +2006,57 @@
         <v>262.7</v>
       </c>
     </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="12"/>
+    </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="N31" t="s">
+      <c r="M31" s="12"/>
+      <c r="N31" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="O31" s="3">
+      <c r="O31" s="8">
         <v>-0.01</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="N32" t="s">
+      <c r="M32" s="12"/>
+      <c r="N32" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="O32" s="5">
+      <c r="O32" s="9">
         <v>0.1</v>
       </c>
     </row>
-    <row r="33" spans="14:15" x14ac:dyDescent="0.25">
-      <c r="N33" t="s">
+    <row r="33" spans="13:15" x14ac:dyDescent="0.25">
+      <c r="M33" s="12"/>
+      <c r="N33" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="O33" s="6">
+      <c r="O33" s="10">
         <f>NPV(O32,J13:DU13)</f>
         <v>2675.5300746330786</v>
       </c>
     </row>
-    <row r="34" spans="14:15" x14ac:dyDescent="0.25">
-      <c r="N34" s="3" t="s">
+    <row r="34" spans="13:15" x14ac:dyDescent="0.25">
+      <c r="M34" s="12"/>
+      <c r="N34" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="O34" s="1">
+      <c r="O34" s="11">
         <f>O33/I15</f>
         <v>13.832747774961632</v>
+      </c>
+    </row>
+    <row r="35" spans="13:15" x14ac:dyDescent="0.25">
+      <c r="M35" s="12"/>
+      <c r="N35" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O35" s="8">
+        <f>Model!O34/Main!K2-1</f>
+        <v>1.0832451468315711</v>
       </c>
     </row>
   </sheetData>
